--- a/imperium-api/generated/quotations/full_quote_test/SNC-FULL-QT-2026-001-R2.xlsx
+++ b/imperium-api/generated/quotations/full_quote_test/SNC-FULL-QT-2026-001-R2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>SIX NINE CONSTRUCTION (PVT) LTD</t>
   </si>
@@ -28,6 +28,9 @@
     <t>Quotation ID: SNC-FULL-QT-2026-001 | Revision: 2</t>
   </si>
   <si>
+    <t>Item No</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -37,10 +40,16 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Total</t>
+    <t>Rate ($)</t>
+  </si>
+  <si>
+    <t>Amount ($)</t>
+  </si>
+  <si>
+    <t>1.0  MEASURED WORKS</t>
+  </si>
+  <si>
+    <t>1.1</t>
   </si>
   <si>
     <t>Site establishment and setting out</t>
@@ -49,33 +58,54 @@
     <t>item</t>
   </si>
   <si>
+    <t>1.2</t>
+  </si>
+  <si>
     <t>Bulk earthworks and cart-away</t>
   </si>
   <si>
     <t>m3</t>
   </si>
   <si>
+    <t>1.3</t>
+  </si>
+  <si>
     <t>Reinforced concrete foundations</t>
   </si>
   <si>
+    <t>1.4</t>
+  </si>
+  <si>
     <t>Structural steel supply and installation</t>
   </si>
   <si>
     <t>ton</t>
   </si>
   <si>
+    <t>1.5</t>
+  </si>
+  <si>
     <t>Roof sheeting and flashings</t>
   </si>
   <si>
     <t>m2</t>
   </si>
   <si>
+    <t>1.6</t>
+  </si>
+  <si>
     <t>Electrical first fix and distribution</t>
   </si>
   <si>
+    <t>1.7</t>
+  </si>
+  <si>
     <t>Plumbing and drainage installation</t>
   </si>
   <si>
+    <t>Measured Works Subtotal:</t>
+  </si>
+  <si>
     <t>Direct Costs:</t>
   </si>
   <si>
@@ -106,44 +136,84 @@
     <t>Assumptions:</t>
   </si>
   <si>
-    <t>- Rates assume normal working hours and unobstructed site access.</t>
-  </si>
-  <si>
-    <t>- Client will provide approved IFC drawings before mobilisation.</t>
-  </si>
-  <si>
-    <t>- Quotation excludes statutory authority fees unless listed separately.</t>
+    <t>• Rates assume normal working hours and unobstructed site access.</t>
+  </si>
+  <si>
+    <t>• Client will provide approved IFC drawings before mobilisation.</t>
+  </si>
+  <si>
+    <t>• Quotation excludes statutory authority fees unless listed separately.</t>
   </si>
   <si>
     <t>Exclusions:</t>
   </si>
   <si>
-    <t>- Rock blasting and contaminated soil remediation.</t>
-  </si>
-  <si>
-    <t>- Client-side professional fees and third-party inspections.</t>
-  </si>
-  <si>
-    <t>- Foreign exchange variation after quote validity period.</t>
-  </si>
-  <si>
-    <t>Audit Trail Hash (Pricing Integrity Key):</t>
-  </si>
-  <si>
-    <t>e75b99239ebf5317b23882c64f8ed16865772bd304b04960f707a6279bb66b7f</t>
+    <t>• Rock blasting and contaminated soil remediation.</t>
+  </si>
+  <si>
+    <t>• Client-side professional fees and third-party inspections.</t>
+  </si>
+  <si>
+    <t>• Foreign exchange variation after quote validity period.</t>
+  </si>
+  <si>
+    <t>Audit Integrity Key:</t>
+  </si>
+  <si>
+    <t>1b14783d1440c39dae2154cbbd478c31f910c1e063d9ce84205680ae0d879ee8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1E293B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -156,16 +226,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,8 +240,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E8F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF08A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -202,15 +282,62 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,34 +632,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="48.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -544,254 +682,302 @@
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
+      <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7">
         <v>1</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E8" s="8">
         <v>2500</v>
       </c>
-      <c r="E7" s="3">
-        <f>C7*D7</f>
+      <c r="F8" s="8">
+        <f>D8*E8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="7">
         <v>850</v>
       </c>
-      <c r="D8" s="3">
+      <c r="E9" s="8">
         <v>12.75</v>
       </c>
-      <c r="E8" s="3">
-        <f>C8*D8</f>
+      <c r="F9" s="8">
+        <f>D9*E9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="7">
+        <v>120</v>
+      </c>
+      <c r="E10" s="8">
+        <v>185.5</v>
+      </c>
+      <c r="F10" s="8">
+        <f>D10*E10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="7">
+        <v>18</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1420</v>
+      </c>
+      <c r="F11" s="8">
+        <f>D11*E11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2200</v>
+      </c>
+      <c r="E12" s="8">
+        <v>18.25</v>
+      </c>
+      <c r="F12" s="8">
+        <f>D12*E12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>120</v>
-      </c>
-      <c r="D9" s="3">
-        <v>185.5</v>
-      </c>
-      <c r="E9" s="3">
-        <f>C9*D9</f>
+      <c r="D13" s="7">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>18750</v>
+      </c>
+      <c r="F13" s="8">
+        <f>D13*E13</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>18</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1420</v>
-      </c>
-      <c r="E10" s="3">
-        <f>C10*D10</f>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8">
+        <v>14200</v>
+      </c>
+      <c r="F14" s="8">
+        <f>D14*E14</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11">
-        <v>2200</v>
-      </c>
-      <c r="D11" s="3">
-        <v>18.25</v>
-      </c>
-      <c r="E11" s="3">
-        <f>C11*D11</f>
+    <row r="15" spans="1:6">
+      <c r="E15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="10">
+        <f>SUM(F8:F14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>18750</v>
-      </c>
-      <c r="E12" s="3">
-        <f>C12*D12</f>
+    <row r="17" spans="1:6">
+      <c r="E17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="8">
+        <f>F15</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>14200</v>
-      </c>
-      <c r="E13" s="3">
-        <f>C13*D13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="D14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="3">
-        <v>134257.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="D15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="3">
+    <row r="18" spans="1:6">
+      <c r="E18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="8">
         <v>9500</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="D16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="3">
+    <row r="19" spans="1:6">
+      <c r="E19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="8">
         <v>10781.81</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="D17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="3">
+    <row r="20" spans="1:6">
+      <c r="E20" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="8">
         <v>9344.24</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="D18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="3">
+    <row r="21" spans="1:6">
+      <c r="E21" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="8">
         <v>17250.9</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="D19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
+    <row r="22" spans="1:6">
+      <c r="E22" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="8">
         <v>15000</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="D20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="3">
+    <row r="23" spans="1:6">
+      <c r="E23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="8">
         <v>2500</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="D21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="3">
-        <v>29045.17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="D22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="3">
-        <v>222679.62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+    <row r="24" spans="1:6">
+      <c r="E24" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="8">
+        <v>30013.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="E25" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="13">
+        <v>223647.79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
-        <v>36</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" t="s">
-        <v>38</v>
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>